--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.37673608742806</v>
+        <v>11.92371961420706</v>
       </c>
       <c r="D2" t="n">
-        <v>73.06347724916554</v>
+        <v>11.8728150529894</v>
       </c>
       <c r="E2" t="n">
-        <v>5.715232076367699</v>
+        <v>0.9287252124097516</v>
       </c>
       <c r="F2" t="n">
-        <v>5.514389277085495</v>
+        <v>0.8960882575263927</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.85868269860426</v>
+        <v>10.53953593852319</v>
       </c>
       <c r="D3" t="n">
-        <v>64.59255491278513</v>
+        <v>10.49629017332759</v>
       </c>
       <c r="E3" t="n">
-        <v>5.715232076367699</v>
+        <v>0.9287252124097516</v>
       </c>
       <c r="F3" t="n">
-        <v>5.514389277085495</v>
+        <v>0.8960882575263927</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.86028269329421</v>
+        <v>10.37729593766031</v>
       </c>
       <c r="D4" t="n">
-        <v>63.52734761760447</v>
+        <v>10.32319398786073</v>
       </c>
       <c r="E4" t="n">
-        <v>5.715232076367699</v>
+        <v>0.9287252124097516</v>
       </c>
       <c r="F4" t="n">
-        <v>5.514389277085495</v>
+        <v>0.8960882575263927</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.30210838014668</v>
+        <v>9.311592611773836</v>
       </c>
       <c r="D5" t="n">
-        <v>57.60778129394029</v>
+        <v>9.361264460265298</v>
       </c>
       <c r="E5" t="n">
-        <v>5.715232076367699</v>
+        <v>0.9287252124097516</v>
       </c>
       <c r="F5" t="n">
-        <v>5.514389277085495</v>
+        <v>0.8960882575263927</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
